--- a/apps/quiz/static/quiz/quiz_import_template.xlsx
+++ b/apps/quiz/static/quiz/quiz_import_template.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,41 +28,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001e293b"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="20"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001e293b"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,26 +41,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001e293b"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00dbeafe"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f1f5f9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f8fafc"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -97,49 +58,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00cbd5e1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00cbd5e1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00cbd5e1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00cbd5e1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,24 +438,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>question_type</t>
@@ -536,56 +469,61 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>option_a</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>option_b</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>option_c</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>option_d</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>option_e</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>correct_option</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>topic_tags</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>year_source</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>mcq / true_false / fill_blank / matching / essay</t>
@@ -596,435 +534,127 @@
           <t>Full question text</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>MCQ: choice A | True/False: leave blank (auto) | Matching: Term→Answer</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Required. Use a consistent label e.g. Chapter 1: Introduction</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MCQ: choice A | True/False: leave blank (auto) | Matching: Term-&gt;Answer</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>MCQ: choice B | True/False: leave blank (auto)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>MCQ: choice C | Matching: Term→Answer pair</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>MCQ: choice C | Matching: Term-&gt;Answer pair</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>MCQ: choice D</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>MCQ: 5th choice (optional)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>MCQ/True-False: a b c d e | Fill blank: answer text | Matching/Essay: leave blank</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Shown to student after answering in practice mode</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>easy / medium / hard  (default: medium)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Comma separated e.g.  OOP, Arrays, Recursion</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Optional comma separated tags e.g. Definition, Basics</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>e.g. 2022</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>mcq</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Which data structure uses LIFO ordering?</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Queue</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Tree</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Graph</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>A stack follows Last In First Out (LIFO) principle.</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Data Structures</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>true_false</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>The time complexity of binary search is O(log n).</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>What is entrepreneurship?</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Chapter 1: Introduction</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>The process of creating value</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>A legal status</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>A business license</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>A government certificate</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Binary search halves the search space each step giving O(log n).</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Entrepreneurship fundamentally involves creating value.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Algorithms</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>fill_blank</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>The process by which plants make food using sunlight is called ___.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>photosynthesis</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>matching</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Match the data structure to its primary use case.</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Stack → Undo operations</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Queue → Print spooling</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>HashMap → Fast lookup</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Tree → Hierarchical data</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Data Structures</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>essay</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Explain the difference between TCP and UDP protocols and give two use cases for each.</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Definition, Basics</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A3:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"mcq,true_false,fill_blank,matching,essay"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J3:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"easy,medium,hard"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>UNIPORTAL — Quiz Import Template</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>HOW TO USE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>1. Fill in the Questions sheet. Row 1 is the header, Row 2 shows notes — do not delete them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2. Start entering your questions from Row 3 onwards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>3. The question_type column has a dropdown — use it to select the correct type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>4. Upload this file in Django Admin → Exam Papers → open the paper → Import Questions from Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="8" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>QUESTION TYPE GUIDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>mcq         →  Fill option_a to option_d (and option_e if 5 choices). Set correct_option to a/b/c/d/e.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>true_false  →  Leave all options blank. Set correct_option to a (True) or b (False).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>fill_blank  →  Leave all options blank. Put the correct answer text in correct_option.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>matching    →  Write each pair in options as  Term → Answer  e.g.  Stack → LIFO. Leave correct_option blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>essay       →  Leave all options and correct_option blank. Add a model answer in explanation if available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>REQUIRED COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>question_type  and  question  are the only required columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>All other columns are optional — blank cells will use defaults (difficulty defaults to medium).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>TOPIC TAGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Enter multiple tags separated by commas.  e.g.   OOP, Inheritance, Polymorphism</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Tags are used in Topic Practice mode to filter questions by subject area.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/apps/quiz/static/quiz/quiz_import_template.xlsx
+++ b/apps/quiz/static/quiz/quiz_import_template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -590,69 +590,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>What is entrepreneurship?</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Chapter 1: Introduction</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>The process of creating value</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>A legal status</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>A business license</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>A government certificate</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Entrepreneurship fundamentally involves creating value.</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Definition, Basics</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
